--- a/Lander DB 251 redux (alt).xlsx
+++ b/Lander DB 251 redux (alt).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\PhD\01_Projects\EUCASS 2025\EUCASS_code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\conal\Desktop\PhD\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B522FFAE-2BDF-44CF-936F-43C17A4AD0AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E69401-8EB1-42F9-ACD3-4A62A1B58040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="2085" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Real Landers" sheetId="1" r:id="rId1"/>
@@ -73,9 +73,9 @@
     </comment>
     <comment ref="E1" authorId="1" shapeId="0" xr:uid="{14C96871-7C53-4D4A-88BE-E5819679F98D}">
       <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     bloc payload is an invented quantity to make 2stage manned landers, 1stage manned landers and 1stage unmanned landers comparable. it's definition is the following
 2stage manned landers: ascent stage mass
 1stage manned landers: landed mass
@@ -463,9 +463,9 @@
     </comment>
     <comment ref="E1" authorId="1" shapeId="0" xr:uid="{F43BA908-11C1-4486-9AC9-41BED78EF776}">
       <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     bloc payload is an invented quantity to make 2stage manned landers, 1stage manned landers and 1stage unmanned landers comparable. it's definition is the following
 2stage manned landers: ascent stage mass
 1stage manned landers: landed mass
@@ -902,9 +902,9 @@
     </comment>
     <comment ref="E1" authorId="1" shapeId="0" xr:uid="{B3F7CD30-2CE1-4425-828F-964D49209C6F}">
       <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     bloc payload is an invented quantity to make 2stage manned landers, 1stage manned landers and 1stage unmanned landers comparable. it's definition is the following
 2stage manned landers: ascent stage mass
 1stage manned landers: landed mass
@@ -1292,9 +1292,9 @@
     </comment>
     <comment ref="E1" authorId="1" shapeId="0" xr:uid="{1825771D-96A2-4E7C-B107-0F2AD72E57AE}">
       <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     bloc payload is an invented quantity to make 2stage manned landers, 1stage manned landers and 1stage unmanned landers comparable. it's definition is the following
 2stage manned landers: ascent stage mass
 1stage manned landers: landed mass
@@ -2209,20 +2209,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.59765625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.86328125" customWidth="1"/>
+    <col min="9" max="9" width="11.3984375" customWidth="1"/>
+    <col min="12" max="12" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" s="14">
         <v>1966</v>
       </c>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="M2" s="4"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="M3" s="4"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" s="5">
         <v>1966</v>
       </c>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="M4" s="4"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" s="8">
         <v>1967</v>
       </c>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="M5" s="4"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" s="5">
         <v>1967</v>
       </c>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="M6" s="4"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="M7" s="4"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="M8" s="4"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" s="5">
         <v>1969</v>
       </c>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" s="8">
         <v>1969</v>
       </c>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="M10" s="4"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" s="8">
         <v>1970</v>
       </c>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="M11" s="4"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" s="5">
         <v>1970</v>
       </c>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="M12" s="4"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" s="5">
         <v>1970</v>
       </c>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="M13" s="4"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" s="8">
         <v>1971</v>
       </c>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M14" s="4"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" s="5">
         <v>1971</v>
       </c>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="M15" s="4"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" s="5">
         <v>1972</v>
       </c>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="M16" s="4"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A17" s="8">
         <v>1972</v>
       </c>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="M17" s="4"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A18" s="5">
         <v>1972</v>
       </c>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="M18" s="4"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A19" s="5">
         <v>1973</v>
       </c>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="M19" s="4"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A20" s="8">
         <v>1976</v>
       </c>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="M20" s="4"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A21" s="5">
         <v>2013</v>
       </c>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="M21" s="4"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A22" s="8">
         <v>2019</v>
       </c>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="M22" s="4"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A23" s="5">
         <v>2019</v>
       </c>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="M23" s="4"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A24" s="8">
         <v>2019</v>
       </c>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M24" s="4"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A25" s="5">
         <v>2020</v>
       </c>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M25" s="4"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A26" s="8">
         <v>2022</v>
       </c>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="M26" s="4"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A27" s="8">
         <v>2023</v>
       </c>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="M27" s="4"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A28" s="8">
         <v>2023</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>8.1105916056322808E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A29" s="5">
         <v>2024</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A30" s="5">
         <v>2024</v>
       </c>
@@ -3504,9 +3504,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9B5FE63-1677-42A4-8B75-DD4C8D8979A4}">
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3544,7 +3544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="11">
         <v>1966</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="8">
         <v>1967</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>0.10855263157894737</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="5">
         <v>1967</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>0.11036789297658862</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>0.10784313725490197</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="8">
         <v>1969</v>
       </c>
@@ -3875,7 +3875,7 @@
         <v>0.70328227571115975</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="5">
         <v>1969</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>0.70319568072377059</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="5">
         <v>1970</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>0.68035768414671116</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" s="5">
         <v>1970</v>
       </c>
@@ -4001,7 +4001,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" s="8">
         <v>1970</v>
       </c>
@@ -4043,7 +4043,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" s="5">
         <v>1971</v>
       </c>
@@ -4085,7 +4085,7 @@
         <v>0.64613933432152004</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" s="8">
         <v>1971</v>
       </c>
@@ -4127,7 +4127,7 @@
         <v>0.68773778167983612</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" s="8">
         <v>1972</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>0.64613933432152004</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" s="5">
         <v>1972</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>0.64613933432152004</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" s="5">
         <v>1972</v>
       </c>
@@ -4253,7 +4253,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" s="5">
         <v>1973</v>
       </c>
@@ -4289,7 +4289,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" s="8">
         <v>1976</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" s="5">
         <v>2013</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" s="8">
         <v>2019</v>
       </c>
@@ -4411,7 +4411,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" s="5">
         <v>2019</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24" s="8">
         <v>2019</v>
       </c>
@@ -4489,7 +4489,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" s="5">
         <v>2020</v>
       </c>
@@ -4529,7 +4529,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26" s="8">
         <v>2022</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" s="8">
         <v>2023</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A28" s="8">
         <v>2023</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A29" s="5">
         <v>2023</v>
       </c>
@@ -4670,7 +4670,7 @@
       <c r="J29" s="7"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A30" s="5">
         <v>2024</v>
       </c>
@@ -4703,7 +4703,7 @@
       <c r="J30" s="10"/>
       <c r="K30" s="3"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A31" s="8">
         <v>2024</v>
       </c>
@@ -4730,7 +4730,7 @@
       <c r="J31" s="7"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A32" s="5">
         <v>2024</v>
       </c>
@@ -4799,12 +4799,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB6D447-256B-4552-8531-20A905B8B356}">
   <dimension ref="A1:L23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4842,7 +4842,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="5">
         <v>1966</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -4967,7 +4967,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="8">
         <v>1967</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>0.10855263157894737</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="5">
         <v>1967</v>
       </c>
@@ -5049,7 +5049,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -5090,7 +5090,7 @@
         <v>0.11036789297658862</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -5131,7 +5131,7 @@
         <v>0.10784313725490197</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="5">
         <v>1970</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="8">
         <v>1970</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="5">
         <v>1972</v>
       </c>
@@ -5257,7 +5257,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" s="5">
         <v>1973</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" s="8">
         <v>1976</v>
       </c>
@@ -5341,7 +5341,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" s="5">
         <v>2013</v>
       </c>
@@ -5381,7 +5381,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" s="8">
         <v>2019</v>
       </c>
@@ -5421,7 +5421,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" s="5">
         <v>2019</v>
       </c>
@@ -5459,7 +5459,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" s="8">
         <v>2019</v>
       </c>
@@ -5499,7 +5499,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" s="5">
         <v>2020</v>
       </c>
@@ -5539,7 +5539,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" s="8">
         <v>2022</v>
       </c>
@@ -5577,7 +5577,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" s="8">
         <v>2023</v>
       </c>
@@ -5615,7 +5615,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" s="8">
         <v>2023</v>
       </c>
@@ -5653,7 +5653,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" s="5">
         <v>2024</v>
       </c>
@@ -5693,7 +5693,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" s="5">
         <v>2024</v>
       </c>
@@ -5778,7 +5778,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21568D6A-64F0-4E55-9F6A-12E6ECCA0346}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5787,9 +5787,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05661A04-FF2A-413A-B709-071725466C45}">
   <dimension ref="A1:L16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5827,7 +5827,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="5">
         <v>1966</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="5">
         <v>1970</v>
       </c>
@@ -5994,7 +5994,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="8">
         <v>1970</v>
       </c>
@@ -6036,7 +6036,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="5">
         <v>1973</v>
       </c>
@@ -6078,7 +6078,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="8">
         <v>1976</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="5">
         <v>2019</v>
       </c>
@@ -6158,7 +6158,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="8">
         <v>2019</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="5">
         <v>2020</v>
       </c>
@@ -6238,7 +6238,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" s="8">
         <v>2022</v>
       </c>
@@ -6276,7 +6276,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" s="8">
         <v>2023</v>
       </c>
@@ -6314,7 +6314,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" s="8">
         <v>2023</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" s="5">
         <v>2024</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" s="5">
         <v>2024</v>
       </c>

--- a/Lander DB 251 redux (alt).xlsx
+++ b/Lander DB 251 redux (alt).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\conal\Desktop\PhD\EUCASS_2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E69401-8EB1-42F9-ACD3-4A62A1B58040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF81D6BF-8632-48F7-BD66-613976C4E442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Real Landers" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Just models" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -73,9 +74,9 @@
     </comment>
     <comment ref="E1" authorId="1" shapeId="0" xr:uid="{14C96871-7C53-4D4A-88BE-E5819679F98D}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Commentaire à thread]
+Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
+Commentaire :
     bloc payload is an invented quantity to make 2stage manned landers, 1stage manned landers and 1stage unmanned landers comparable. it's definition is the following
 2stage manned landers: ascent stage mass
 1stage manned landers: landed mass
@@ -463,9 +464,9 @@
     </comment>
     <comment ref="E1" authorId="1" shapeId="0" xr:uid="{F43BA908-11C1-4486-9AC9-41BED78EF776}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Commentaire à thread]
+Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
+Commentaire :
     bloc payload is an invented quantity to make 2stage manned landers, 1stage manned landers and 1stage unmanned landers comparable. it's definition is the following
 2stage manned landers: ascent stage mass
 1stage manned landers: landed mass
@@ -902,9 +903,9 @@
     </comment>
     <comment ref="E1" authorId="1" shapeId="0" xr:uid="{B3F7CD30-2CE1-4425-828F-964D49209C6F}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Commentaire à thread]
+Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
+Commentaire :
     bloc payload is an invented quantity to make 2stage manned landers, 1stage manned landers and 1stage unmanned landers comparable. it's definition is the following
 2stage manned landers: ascent stage mass
 1stage manned landers: landed mass
@@ -1292,9 +1293,9 @@
     </comment>
     <comment ref="E1" authorId="1" shapeId="0" xr:uid="{1825771D-96A2-4E7C-B107-0F2AD72E57AE}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Commentaire à thread]
+Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
+Commentaire :
     bloc payload is an invented quantity to make 2stage manned landers, 1stage manned landers and 1stage unmanned landers comparable. it's definition is the following
 2stage manned landers: ascent stage mass
 1stage manned landers: landed mass
@@ -2209,20 +2210,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.73046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.86328125" customWidth="1"/>
-    <col min="9" max="9" width="11.3984375" customWidth="1"/>
-    <col min="12" max="12" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2260,7 +2261,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="14">
         <v>1966</v>
       </c>
@@ -2302,7 +2303,7 @@
       </c>
       <c r="M2" s="4"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -2345,7 +2346,7 @@
       </c>
       <c r="M3" s="4"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>1966</v>
       </c>
@@ -2388,7 +2389,7 @@
       </c>
       <c r="M4" s="4"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>1967</v>
       </c>
@@ -2430,7 +2431,7 @@
       </c>
       <c r="M5" s="4"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>1967</v>
       </c>
@@ -2472,7 +2473,7 @@
       </c>
       <c r="M6" s="4"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -2514,7 +2515,7 @@
       </c>
       <c r="M7" s="4"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -2556,7 +2557,7 @@
       </c>
       <c r="M8" s="4"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>1969</v>
       </c>
@@ -2599,7 +2600,7 @@
       </c>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>1969</v>
       </c>
@@ -2642,7 +2643,7 @@
       </c>
       <c r="M10" s="4"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>1970</v>
       </c>
@@ -2685,7 +2686,7 @@
       </c>
       <c r="M11" s="4"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>1970</v>
       </c>
@@ -2728,7 +2729,7 @@
       </c>
       <c r="M12" s="4"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>1970</v>
       </c>
@@ -2771,7 +2772,7 @@
       </c>
       <c r="M13" s="4"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>1971</v>
       </c>
@@ -2814,7 +2815,7 @@
       </c>
       <c r="M14" s="4"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>1971</v>
       </c>
@@ -2857,7 +2858,7 @@
       </c>
       <c r="M15" s="4"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>1972</v>
       </c>
@@ -2900,7 +2901,7 @@
       </c>
       <c r="M16" s="4"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>1972</v>
       </c>
@@ -2943,7 +2944,7 @@
       </c>
       <c r="M17" s="4"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>1972</v>
       </c>
@@ -2986,7 +2987,7 @@
       </c>
       <c r="M18" s="4"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>1973</v>
       </c>
@@ -3027,7 +3028,7 @@
       </c>
       <c r="M19" s="4"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>1976</v>
       </c>
@@ -3070,7 +3071,7 @@
       </c>
       <c r="M20" s="4"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>2013</v>
       </c>
@@ -3111,7 +3112,7 @@
       </c>
       <c r="M21" s="4"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>2019</v>
       </c>
@@ -3152,7 +3153,7 @@
       </c>
       <c r="M22" s="4"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>2019</v>
       </c>
@@ -3193,7 +3194,7 @@
       </c>
       <c r="M23" s="4"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>2019</v>
       </c>
@@ -3234,7 +3235,7 @@
       </c>
       <c r="M24" s="4"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>2020</v>
       </c>
@@ -3275,7 +3276,7 @@
       </c>
       <c r="M25" s="4"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>2022</v>
       </c>
@@ -3316,7 +3317,7 @@
       </c>
       <c r="M26" s="4"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>2023</v>
       </c>
@@ -3357,7 +3358,7 @@
       </c>
       <c r="M27" s="4"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>2023</v>
       </c>
@@ -3397,7 +3398,7 @@
         <v>8.1105916056322808E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>2024</v>
       </c>
@@ -3437,7 +3438,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>2024</v>
       </c>
@@ -3504,9 +3505,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9B5FE63-1677-42A4-8B75-DD4C8D8979A4}">
   <dimension ref="A1:L32"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3544,7 +3545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="11">
         <v>1966</v>
       </c>
@@ -3586,7 +3587,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -3628,7 +3629,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -3669,7 +3670,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>1967</v>
       </c>
@@ -3710,7 +3711,7 @@
         <v>0.10855263157894737</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>1967</v>
       </c>
@@ -3751,7 +3752,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -3792,7 +3793,7 @@
         <v>0.11036789297658862</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -3833,7 +3834,7 @@
         <v>0.10784313725490197</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>1969</v>
       </c>
@@ -3875,7 +3876,7 @@
         <v>0.70328227571115975</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>1969</v>
       </c>
@@ -3917,7 +3918,7 @@
         <v>0.70319568072377059</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>1970</v>
       </c>
@@ -3959,7 +3960,7 @@
         <v>0.68035768414671116</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>1970</v>
       </c>
@@ -4001,7 +4002,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>1970</v>
       </c>
@@ -4043,7 +4044,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>1971</v>
       </c>
@@ -4085,7 +4086,7 @@
         <v>0.64613933432152004</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>1971</v>
       </c>
@@ -4127,7 +4128,7 @@
         <v>0.68773778167983612</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>1972</v>
       </c>
@@ -4169,7 +4170,7 @@
         <v>0.64613933432152004</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>1972</v>
       </c>
@@ -4211,7 +4212,7 @@
         <v>0.64613933432152004</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>1972</v>
       </c>
@@ -4253,7 +4254,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>1973</v>
       </c>
@@ -4289,7 +4290,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>1976</v>
       </c>
@@ -4331,7 +4332,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>2013</v>
       </c>
@@ -4371,7 +4372,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>2019</v>
       </c>
@@ -4411,7 +4412,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>2019</v>
       </c>
@@ -4449,7 +4450,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>2019</v>
       </c>
@@ -4489,7 +4490,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>2020</v>
       </c>
@@ -4529,7 +4530,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>2022</v>
       </c>
@@ -4567,7 +4568,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>2023</v>
       </c>
@@ -4605,7 +4606,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>2023</v>
       </c>
@@ -4643,7 +4644,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>2023</v>
       </c>
@@ -4670,7 +4671,7 @@
       <c r="J29" s="7"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>2024</v>
       </c>
@@ -4703,7 +4704,7 @@
       <c r="J30" s="10"/>
       <c r="K30" s="3"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>2024</v>
       </c>
@@ -4730,7 +4731,7 @@
       <c r="J31" s="7"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>2024</v>
       </c>
@@ -4799,12 +4800,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB6D447-256B-4552-8531-20A905B8B356}">
   <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4842,7 +4843,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1966</v>
       </c>
@@ -4884,7 +4885,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -4926,7 +4927,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -4967,7 +4968,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>1967</v>
       </c>
@@ -5008,7 +5009,7 @@
         <v>0.10855263157894737</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>1967</v>
       </c>
@@ -5049,7 +5050,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -5090,7 +5091,7 @@
         <v>0.11036789297658862</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -5131,7 +5132,7 @@
         <v>0.10784313725490197</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>1970</v>
       </c>
@@ -5173,7 +5174,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>1970</v>
       </c>
@@ -5215,7 +5216,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>1972</v>
       </c>
@@ -5257,7 +5258,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>1973</v>
       </c>
@@ -5299,7 +5300,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>1976</v>
       </c>
@@ -5341,7 +5342,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>2013</v>
       </c>
@@ -5381,7 +5382,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>2019</v>
       </c>
@@ -5421,7 +5422,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>2019</v>
       </c>
@@ -5459,7 +5460,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>2019</v>
       </c>
@@ -5499,7 +5500,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>2020</v>
       </c>
@@ -5539,7 +5540,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>2022</v>
       </c>
@@ -5577,7 +5578,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>2023</v>
       </c>
@@ -5615,7 +5616,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>2023</v>
       </c>
@@ -5653,7 +5654,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>2024</v>
       </c>
@@ -5693,7 +5694,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>2024</v>
       </c>
@@ -5778,7 +5779,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21568D6A-64F0-4E55-9F6A-12E6ECCA0346}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5787,9 +5788,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05661A04-FF2A-413A-B709-071725466C45}">
   <dimension ref="A1:L16"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5827,7 +5828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1966</v>
       </c>
@@ -5869,7 +5870,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -5911,7 +5912,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -5952,7 +5953,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>1970</v>
       </c>
@@ -5994,7 +5995,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>1970</v>
       </c>
@@ -6036,7 +6037,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1973</v>
       </c>
@@ -6078,7 +6079,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>1976</v>
       </c>
@@ -6120,7 +6121,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>2019</v>
       </c>
@@ -6158,7 +6159,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>2019</v>
       </c>
@@ -6198,7 +6199,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>2020</v>
       </c>
@@ -6238,7 +6239,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>2022</v>
       </c>
@@ -6276,7 +6277,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>2023</v>
       </c>
@@ -6314,7 +6315,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>2023</v>
       </c>
@@ -6352,7 +6353,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>2024</v>
       </c>
@@ -6392,7 +6393,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>2024</v>
       </c>

--- a/Lander DB 251 redux (alt).xlsx
+++ b/Lander DB 251 redux (alt).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF81D6BF-8632-48F7-BD66-613976C4E442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17EFF34B-4E78-4007-9F85-8F9F17E049BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,6 @@
     <sheet name="Just models" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1553,7 +1552,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="63">
   <si>
     <t>year</t>
   </si>
@@ -1731,6 +1730,18 @@
   <si>
     <t>minert</t>
   </si>
+  <si>
+    <t>Chang'e 6</t>
+  </si>
+  <si>
+    <t>Blueghost</t>
+  </si>
+  <si>
+    <t>Athena</t>
+  </si>
+  <si>
+    <t>Hakuto-R M2</t>
+  </si>
 </sst>
 </file>
 
@@ -1835,7 +1846,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1868,13 +1879,14 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2209,12 +2221,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
@@ -2223,7 +2235,7 @@
     <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2261,79 +2273,78 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="14">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="15">
         <v>1966</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="15">
         <v>995.2</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="15">
         <v>262</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="15">
         <v>33</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="15">
         <f t="shared" ref="F2:F10" si="0">C2-D2-E2</f>
         <v>700.2</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="15">
         <v>295</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="15">
         <v>230</v>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="15">
         <v>2612</v>
       </c>
       <c r="K2" s="3">
-        <f t="shared" ref="K2:K29" si="1">E2/D2</f>
+        <f t="shared" ref="K2:K34" si="1">E2/D2</f>
         <v>0.12595419847328243</v>
       </c>
       <c r="L2" s="3">
-        <f t="shared" ref="L2:L29" si="2">E2/(D2+E2)</f>
+        <f t="shared" ref="L2:L34" si="2">E2/(D2+E2)</f>
         <v>0.11186440677966102</v>
       </c>
-      <c r="M2" s="4"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <v>1966</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="5">
         <v>1538</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="5">
         <v>847</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="5">
         <v>99.8</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="5">
         <f t="shared" si="0"/>
         <v>591.20000000000005</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="5">
         <f>C3-F3</f>
         <v>946.8</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="5">
         <v>287</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="5">
         <v>2630</v>
       </c>
       <c r="K3" s="3">
@@ -2344,39 +2355,38 @@
         <f t="shared" si="2"/>
         <v>0.10540768905787917</v>
       </c>
-      <c r="M3" s="4"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="14">
         <v>1966</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="14">
         <v>1620</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="14">
         <v>800</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="14">
         <v>112</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="14">
         <f t="shared" si="0"/>
         <v>708</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="14">
         <f>C4-F4</f>
         <v>912</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="14">
         <v>287</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="14">
         <v>1880</v>
       </c>
       <c r="K4" s="3">
@@ -2387,38 +2397,37 @@
         <f t="shared" si="2"/>
         <v>0.12280701754385964</v>
       </c>
-      <c r="M4" s="4"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <v>1967</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="5">
         <v>1006</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="5">
         <v>271</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="5">
         <v>33.01</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="5">
         <f t="shared" si="0"/>
         <v>701.99</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="5">
         <v>304</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="5">
         <v>230</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="5">
         <v>2612</v>
       </c>
       <c r="K5" s="3">
@@ -2429,38 +2438,37 @@
         <f t="shared" si="2"/>
         <v>0.10858195454096904</v>
       </c>
-      <c r="M5" s="4"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="14">
         <v>1967</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="14">
         <v>1026</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="14">
         <v>267</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="14">
         <v>33.020000000000003</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="14">
         <f t="shared" si="0"/>
         <v>725.98</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="14">
         <v>300</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="14">
         <v>230</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="14">
         <v>2612</v>
       </c>
       <c r="K6" s="3">
@@ -2471,9 +2479,8 @@
         <f t="shared" si="2"/>
         <v>0.11005932937804148</v>
       </c>
-      <c r="M6" s="4"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -2502,7 +2509,7 @@
       <c r="I7" s="5">
         <v>230</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="5">
         <v>2612</v>
       </c>
       <c r="K7" s="3">
@@ -2513,38 +2520,37 @@
         <f t="shared" si="2"/>
         <v>0.11045714476808348</v>
       </c>
-      <c r="M7" s="4"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="14">
         <v>1968</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="14">
         <v>1039</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="14">
         <v>273</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="14">
         <v>33.04</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="14">
         <f t="shared" si="0"/>
         <v>732.96</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="14">
         <v>306</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="14">
         <v>230</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="14">
         <v>2612</v>
       </c>
       <c r="K8" s="3">
@@ -2555,9 +2561,8 @@
         <f t="shared" si="2"/>
         <v>0.10795974382433668</v>
       </c>
-      <c r="M8" s="4"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>1969</v>
       </c>
@@ -2567,7 +2572,7 @@
       <c r="C9" s="5">
         <v>15065</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="5">
         <v>2034</v>
       </c>
       <c r="E9" s="5">
@@ -2598,39 +2603,38 @@
         <f t="shared" si="2"/>
         <v>0.70319568072377059</v>
       </c>
-      <c r="M9" s="4"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="14">
         <v>1969</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="14">
         <v>15103</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="14">
         <v>2034</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="14">
         <v>4821</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="14">
         <f t="shared" si="0"/>
         <v>8248</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="14">
         <f>C10-F10</f>
         <v>6855</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="14">
         <v>311</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="14">
         <v>2261</v>
       </c>
       <c r="K10" s="3">
@@ -2641,39 +2645,38 @@
         <f t="shared" si="2"/>
         <v>0.70328227571115975</v>
       </c>
-      <c r="M10" s="4"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <v>1970</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="5">
         <v>5727</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <f>G11-E11</f>
         <v>1360</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="5">
         <v>520</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="5">
         <f>C11-G11</f>
         <v>3847</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="5">
         <v>1880</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="5">
         <v>314</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="5">
         <v>1880</v>
       </c>
       <c r="K11" s="3">
@@ -2684,39 +2687,38 @@
         <f t="shared" si="2"/>
         <v>0.27659574468085107</v>
       </c>
-      <c r="M11" s="4"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="14">
         <v>1970</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="14">
         <v>5660</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="14">
         <f>G12-E12</f>
         <v>1144</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="14">
         <v>756</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="14">
         <f>C12-D12-E12</f>
         <v>3760</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="14">
         <v>1900</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="14">
         <v>314</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="14">
         <v>1880</v>
       </c>
       <c r="K12" s="3">
@@ -2727,9 +2729,8 @@
         <f t="shared" si="2"/>
         <v>0.39789473684210525</v>
       </c>
-      <c r="M12" s="4"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>1970</v>
       </c>
@@ -2770,39 +2771,38 @@
         <f t="shared" si="2"/>
         <v>0.68035768414671116</v>
       </c>
-      <c r="M13" s="4"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="14">
         <v>1971</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="14">
         <v>15034</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="14">
         <v>2134</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="14">
         <v>4700</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="14">
         <f>C14-D14-E14</f>
         <v>8200</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="14">
         <f>C14-F14</f>
         <v>6834</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="14">
         <v>311</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="14">
         <v>2263</v>
       </c>
       <c r="K14" s="3">
@@ -2813,9 +2813,8 @@
         <f t="shared" si="2"/>
         <v>0.68773778167983612</v>
       </c>
-      <c r="M14" s="4"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>1971</v>
       </c>
@@ -2856,39 +2855,38 @@
         <f t="shared" si="2"/>
         <v>0.64613933432152004</v>
       </c>
-      <c r="M15" s="4"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="5">
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="14">
         <v>1972</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="14">
         <v>5750</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="14">
         <f>G16-E16</f>
         <v>1359.99</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="14">
         <v>520.01</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="14">
         <f>C16-G16</f>
         <v>3870</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="14">
         <v>1880</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="14">
         <v>314</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J16" s="14">
         <v>1880</v>
       </c>
       <c r="K16" s="3">
@@ -2899,39 +2897,38 @@
         <f t="shared" si="2"/>
         <v>0.27660106382978722</v>
       </c>
-      <c r="M16" s="4"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <v>1972</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="5">
         <v>16447</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="5">
         <v>2626</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="5">
         <v>4795.01</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="5">
         <f>C17-D17-E17</f>
         <v>9025.99</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="5">
         <f>C17-F17</f>
         <v>7421.01</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="5">
         <v>311</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="5">
         <v>2267</v>
       </c>
       <c r="K17" s="3">
@@ -2942,39 +2939,38 @@
         <f t="shared" si="2"/>
         <v>0.64613981115778041</v>
       </c>
-      <c r="M17" s="4"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="5">
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="14">
         <v>1972</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="14">
         <v>16447</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="14">
         <v>2626</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="14">
         <v>4795.0200000000004</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="14">
         <f>C18-D18-E18</f>
         <v>9025.98</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="14">
         <f>C18-F18</f>
         <v>7421.02</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="14">
         <v>311</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J18" s="14">
         <v>2265</v>
       </c>
       <c r="K18" s="3">
@@ -2985,9 +2981,8 @@
         <f t="shared" si="2"/>
         <v>0.64614028799275569</v>
       </c>
-      <c r="M18" s="4"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>1973</v>
       </c>
@@ -3011,7 +3006,9 @@
       <c r="G19" s="5">
         <v>1836</v>
       </c>
-      <c r="H19" s="5"/>
+      <c r="H19" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="I19" s="5">
         <v>314</v>
       </c>
@@ -3026,39 +3023,38 @@
         <f t="shared" si="2"/>
         <v>0.45533769063180829</v>
       </c>
-      <c r="M19" s="4"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="8">
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="14">
         <v>1976</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="14">
         <v>5795</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="14">
         <f>G20-E20</f>
         <v>1365</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="14">
         <v>515</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="14">
         <f>C20-G20</f>
         <v>3915</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="14">
         <v>1880</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="14">
         <v>314</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="14">
         <v>1880</v>
       </c>
       <c r="K20" s="3">
@@ -3069,9 +3065,8 @@
         <f t="shared" si="2"/>
         <v>0.27393617021276595</v>
       </c>
-      <c r="M20" s="4"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>2013</v>
       </c>
@@ -3110,37 +3105,36 @@
         <f t="shared" si="2"/>
         <v>0.12408759124087591</v>
       </c>
-      <c r="M21" s="4"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="8">
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="14">
         <v>2019</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="14">
         <v>585</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="14">
         <v>150</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="14">
         <v>0.1</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="14">
         <v>435</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="14">
         <v>150</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="14">
         <v>318</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="14">
         <v>1930</v>
       </c>
       <c r="K22" s="3">
@@ -3151,9 +3145,8 @@
         <f t="shared" si="2"/>
         <v>6.6622251832111927E-4</v>
       </c>
-      <c r="M22" s="4"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>2019</v>
       </c>
@@ -3181,7 +3174,7 @@
       <c r="I23" s="5">
         <v>318</v>
       </c>
-      <c r="J23" s="7">
+      <c r="J23" s="5">
         <v>2000</v>
       </c>
       <c r="K23" s="3">
@@ -3192,37 +3185,36 @@
         <f t="shared" si="2"/>
         <v>4.1347626339969371E-2</v>
       </c>
-      <c r="M23" s="4"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="8">
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="14">
         <v>2019</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="14">
         <v>3640</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="14">
         <v>1200</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="14">
         <v>170.01</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="14">
         <v>2270</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="14">
         <v>1370</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="14">
         <v>333</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="14">
         <v>1880</v>
       </c>
       <c r="K24" s="3">
@@ -3233,9 +3225,8 @@
         <f t="shared" si="2"/>
         <v>0.12409398471544003</v>
       </c>
-      <c r="M24" s="4"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>2020</v>
       </c>
@@ -3274,37 +3265,36 @@
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
-      <c r="M25" s="4"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="8">
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="14">
         <v>2022</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="14">
         <v>14.6</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="14">
         <v>0.7</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="14">
         <v>0.10100000000000001</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="14">
         <v>13.9</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="14">
         <v>0.69999999999999929</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="14">
         <v>287</v>
       </c>
-      <c r="J26" s="8">
+      <c r="J26" s="14">
         <v>2500</v>
       </c>
       <c r="K26" s="3">
@@ -3315,37 +3305,36 @@
         <f t="shared" si="2"/>
         <v>0.12609238451935084</v>
       </c>
-      <c r="M26" s="4"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="8">
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
         <v>2023</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="5">
         <v>1750</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="5">
         <v>770</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="5">
         <v>30</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="5">
         <v>950</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="5">
         <v>800</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="5">
         <v>333</v>
       </c>
-      <c r="J27" s="7">
+      <c r="J27" s="5">
         <v>2000</v>
       </c>
       <c r="K27" s="3">
@@ -3356,37 +3345,36 @@
         <f t="shared" si="2"/>
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="M27" s="4"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" s="8">
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="14">
         <v>2023</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="14">
         <v>1000</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="14">
         <v>340</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="14">
         <v>30.01</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="14">
         <v>630</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="14">
         <v>370</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="I28" s="8">
-        <v>333</v>
-      </c>
-      <c r="J28" s="7">
+      <c r="I28" s="14">
+        <v>336</v>
+      </c>
+      <c r="J28" s="14">
         <v>2000</v>
       </c>
       <c r="K28" s="3">
@@ -3398,7 +3386,7 @@
         <v>8.1105916056322808E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>2024</v>
       </c>
@@ -3438,47 +3426,213 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A30" s="5">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="14">
         <v>2024</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="14">
         <v>1908</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="14">
         <f>675-E30</f>
         <v>545</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="14">
         <v>130</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="14">
         <v>1276</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="14">
         <f>675</f>
         <v>675</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I30" s="14">
         <v>360</v>
       </c>
-      <c r="J30" s="10">
+      <c r="J30" s="14">
         <v>2500</v>
       </c>
-      <c r="K30" s="3"/>
+      <c r="K30" s="3">
+        <f t="shared" si="1"/>
+        <v>0.23853211009174313</v>
+      </c>
+      <c r="L30" s="3">
+        <f t="shared" si="2"/>
+        <v>0.19259259259259259</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="5">
+        <v>2024</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="5">
+        <v>3800</v>
+      </c>
+      <c r="D31" s="5">
+        <v>1200</v>
+      </c>
+      <c r="E31" s="5">
+        <v>800</v>
+      </c>
+      <c r="F31" s="5">
+        <v>1800</v>
+      </c>
+      <c r="G31" s="5">
+        <v>2000</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I31" s="5">
+        <v>333</v>
+      </c>
+      <c r="J31" s="5"/>
+      <c r="K31" s="3">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="L31" s="3">
+        <f t="shared" si="2"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="14">
+        <v>1517</v>
+      </c>
+      <c r="D32" s="14">
+        <f>C32-E32-F32</f>
+        <v>331</v>
+      </c>
+      <c r="E32" s="14">
+        <v>150</v>
+      </c>
+      <c r="F32" s="14">
+        <v>1036</v>
+      </c>
+      <c r="G32" s="14">
+        <f>C32-F32</f>
+        <v>481</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="I32" s="14">
+        <v>340</v>
+      </c>
+      <c r="J32" s="14"/>
+      <c r="K32" s="3">
+        <f t="shared" si="1"/>
+        <v>0.45317220543806647</v>
+      </c>
+      <c r="L32" s="3">
+        <f t="shared" si="2"/>
+        <v>0.31185031185031187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="5">
+        <v>2120</v>
+      </c>
+      <c r="D33" s="5">
+        <f>675-130</f>
+        <v>545</v>
+      </c>
+      <c r="E33" s="5">
+        <v>130</v>
+      </c>
+      <c r="F33" s="5">
+        <f>C33-D33-E33</f>
+        <v>1445</v>
+      </c>
+      <c r="G33" s="5">
+        <f>C33-F33</f>
+        <v>675</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I33" s="5">
+        <v>360</v>
+      </c>
+      <c r="J33" s="5"/>
+      <c r="K33" s="3">
+        <f t="shared" si="1"/>
+        <v>0.23853211009174313</v>
+      </c>
+      <c r="L33" s="3">
+        <f t="shared" si="2"/>
+        <v>0.19259259259259259</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="14">
+        <v>1000</v>
+      </c>
+      <c r="D34" s="14">
+        <v>340</v>
+      </c>
+      <c r="E34" s="14">
+        <v>30</v>
+      </c>
+      <c r="F34" s="14">
+        <f>C34-E34-D34</f>
+        <v>630</v>
+      </c>
+      <c r="G34" s="14">
+        <f>C34-F34</f>
+        <v>370</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="14">
+        <v>336</v>
+      </c>
+      <c r="J34" s="14"/>
+      <c r="K34" s="3">
+        <f t="shared" si="1"/>
+        <v>8.8235294117647065E-2</v>
+      </c>
+      <c r="L34" s="3">
+        <f t="shared" si="2"/>
+        <v>8.1081081081081086E-2</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L30">
     <sortCondition ref="A2:A30"/>
   </sortState>
-  <conditionalFormatting sqref="K2:K30">
-    <cfRule type="colorScale" priority="21">
+  <conditionalFormatting sqref="K2:K34">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3488,7 +3642,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="22">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>

--- a/Lander DB 251 redux (alt).xlsx
+++ b/Lander DB 251 redux (alt).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17EFF34B-4E78-4007-9F85-8F9F17E049BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6769C7C0-7D64-4E33-AFB1-18411BC3F5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1846,7 +1846,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1879,14 +1879,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2274,43 +2270,43 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="15">
+      <c r="A2" s="14">
         <v>1966</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="14">
         <v>995.2</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="14">
         <v>262</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="14">
         <v>33</v>
       </c>
-      <c r="F2" s="15">
-        <f t="shared" ref="F2:F10" si="0">C2-D2-E2</f>
+      <c r="F2" s="14">
+        <f>C2-D2-E2</f>
         <v>700.2</v>
       </c>
-      <c r="G2" s="15">
+      <c r="G2" s="14">
         <v>295</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="15">
+      <c r="I2" s="14">
         <v>230</v>
       </c>
-      <c r="J2" s="15">
+      <c r="J2" s="14">
         <v>2612</v>
       </c>
       <c r="K2" s="3">
-        <f t="shared" ref="K2:K34" si="1">E2/D2</f>
+        <f>E2/D2</f>
         <v>0.12595419847328243</v>
       </c>
       <c r="L2" s="3">
-        <f t="shared" ref="L2:L34" si="2">E2/(D2+E2)</f>
+        <f>E2/(D2+E2)</f>
         <v>0.11186440677966102</v>
       </c>
     </row>
@@ -2331,7 +2327,7 @@
         <v>99.8</v>
       </c>
       <c r="F3" s="5">
-        <f t="shared" si="0"/>
+        <f>C3-D3-E3</f>
         <v>591.20000000000005</v>
       </c>
       <c r="G3" s="5">
@@ -2348,53 +2344,53 @@
         <v>2630</v>
       </c>
       <c r="K3" s="3">
-        <f t="shared" si="1"/>
+        <f>E3/D3</f>
         <v>0.117827626918536</v>
       </c>
       <c r="L3" s="3">
-        <f t="shared" si="2"/>
+        <f>E3/(D3+E3)</f>
         <v>0.10540768905787917</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="14">
+      <c r="A4" s="8">
         <v>1966</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="8">
         <v>1620</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="8">
         <v>800</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="8">
         <v>112</v>
       </c>
-      <c r="F4" s="14">
-        <f t="shared" si="0"/>
+      <c r="F4" s="8">
+        <f>C4-D4-E4</f>
         <v>708</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="8">
         <f>C4-F4</f>
         <v>912</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="8">
         <v>287</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="8">
         <v>1880</v>
       </c>
       <c r="K4" s="3">
-        <f t="shared" si="1"/>
+        <f>E4/D4</f>
         <v>0.14000000000000001</v>
       </c>
       <c r="L4" s="3">
-        <f t="shared" si="2"/>
+        <f>E4/(D4+E4)</f>
         <v>0.12280701754385964</v>
       </c>
     </row>
@@ -2415,7 +2411,7 @@
         <v>33.01</v>
       </c>
       <c r="F5" s="5">
-        <f t="shared" si="0"/>
+        <f>C5-D5-E5</f>
         <v>701.99</v>
       </c>
       <c r="G5" s="5">
@@ -2431,52 +2427,52 @@
         <v>2612</v>
       </c>
       <c r="K5" s="3">
-        <f t="shared" si="1"/>
+        <f>E5/D5</f>
         <v>0.12180811808118081</v>
       </c>
       <c r="L5" s="3">
-        <f t="shared" si="2"/>
+        <f>E5/(D5+E5)</f>
         <v>0.10858195454096904</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="14">
+      <c r="A6" s="8">
         <v>1967</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="8">
         <v>1026</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="8">
         <v>267</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="8">
         <v>33.020000000000003</v>
       </c>
-      <c r="F6" s="14">
-        <f t="shared" si="0"/>
+      <c r="F6" s="8">
+        <f>C6-D6-E6</f>
         <v>725.98</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="8">
         <v>300</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="8">
         <v>230</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="8">
         <v>2612</v>
       </c>
       <c r="K6" s="3">
-        <f t="shared" si="1"/>
+        <f>E6/D6</f>
         <v>0.12367041198501874</v>
       </c>
       <c r="L6" s="3">
-        <f t="shared" si="2"/>
+        <f>E6/(D6+E6)</f>
         <v>0.11005932937804148</v>
       </c>
     </row>
@@ -2497,7 +2493,7 @@
         <v>33.03</v>
       </c>
       <c r="F7" s="5">
-        <f t="shared" si="0"/>
+        <f>C7-D7-E7</f>
         <v>726.97</v>
       </c>
       <c r="G7" s="5">
@@ -2513,52 +2509,52 @@
         <v>2612</v>
       </c>
       <c r="K7" s="3">
-        <f t="shared" si="1"/>
+        <f>E7/D7</f>
         <v>0.12417293233082707</v>
       </c>
       <c r="L7" s="3">
-        <f t="shared" si="2"/>
+        <f>E7/(D7+E7)</f>
         <v>0.11045714476808348</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="14">
+      <c r="A8" s="8">
         <v>1968</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="8">
         <v>1039</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="8">
         <v>273</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="8">
         <v>33.04</v>
       </c>
-      <c r="F8" s="14">
-        <f t="shared" si="0"/>
+      <c r="F8" s="8">
+        <f>C8-D8-E8</f>
         <v>732.96</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="8">
         <v>306</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="8">
         <v>230</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="8">
         <v>2612</v>
       </c>
       <c r="K8" s="3">
-        <f t="shared" si="1"/>
+        <f>E8/D8</f>
         <v>0.12102564102564102</v>
       </c>
       <c r="L8" s="3">
-        <f t="shared" si="2"/>
+        <f>E8/(D8+E8)</f>
         <v>0.10795974382433668</v>
       </c>
     </row>
@@ -2579,7 +2575,7 @@
         <v>4819</v>
       </c>
       <c r="F9" s="5">
-        <f t="shared" si="0"/>
+        <f>C9-D9-E9</f>
         <v>8212</v>
       </c>
       <c r="G9" s="5">
@@ -2596,53 +2592,53 @@
         <v>2273</v>
       </c>
       <c r="K9" s="3">
-        <f t="shared" si="1"/>
+        <f>E9/D9</f>
         <v>2.3692232055063913</v>
       </c>
       <c r="L9" s="3">
-        <f t="shared" si="2"/>
+        <f>E9/(D9+E9)</f>
         <v>0.70319568072377059</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="14">
+      <c r="A10" s="8">
         <v>1969</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="8">
         <v>15103</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="8">
         <v>2034</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="8">
         <v>4821</v>
       </c>
-      <c r="F10" s="14">
-        <f t="shared" si="0"/>
+      <c r="F10" s="8">
+        <f>C10-D10-E10</f>
         <v>8248</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="8">
         <f>C10-F10</f>
         <v>6855</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="8">
         <v>311</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="8">
         <v>2261</v>
       </c>
       <c r="K10" s="3">
-        <f t="shared" si="1"/>
+        <f>E10/D10</f>
         <v>2.3702064896755162</v>
       </c>
       <c r="L10" s="3">
-        <f t="shared" si="2"/>
+        <f>E10/(D10+E10)</f>
         <v>0.70328227571115975</v>
       </c>
     </row>
@@ -2680,53 +2676,53 @@
         <v>1880</v>
       </c>
       <c r="K11" s="3">
-        <f t="shared" si="1"/>
+        <f>E11/D11</f>
         <v>0.38235294117647056</v>
       </c>
       <c r="L11" s="3">
-        <f t="shared" si="2"/>
+        <f>E11/(D11+E11)</f>
         <v>0.27659574468085107</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="14">
+      <c r="A12" s="8">
         <v>1970</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="8">
         <v>5660</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="8">
         <f>G12-E12</f>
         <v>1144</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="8">
         <v>756</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="8">
         <f>C12-D12-E12</f>
         <v>3760</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="8">
         <v>1900</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="8">
         <v>314</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="8">
         <v>1880</v>
       </c>
       <c r="K12" s="3">
-        <f t="shared" si="1"/>
+        <f>E12/D12</f>
         <v>0.66083916083916083</v>
       </c>
       <c r="L12" s="3">
-        <f t="shared" si="2"/>
+        <f>E12/(D12+E12)</f>
         <v>0.39789473684210525</v>
       </c>
     </row>
@@ -2764,53 +2760,53 @@
         <v>2263</v>
       </c>
       <c r="K13" s="3">
-        <f t="shared" si="1"/>
+        <f>E13/D13</f>
         <v>2.1284969179706024</v>
       </c>
       <c r="L13" s="3">
-        <f t="shared" si="2"/>
+        <f>E13/(D13+E13)</f>
         <v>0.68035768414671116</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="14">
+      <c r="A14" s="8">
         <v>1971</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="8">
         <v>15034</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="8">
         <v>2134</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="8">
         <v>4700</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="8">
         <f>C14-D14-E14</f>
         <v>8200</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="8">
         <f>C14-F14</f>
         <v>6834</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="8">
         <v>311</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="8">
         <v>2263</v>
       </c>
       <c r="K14" s="3">
-        <f t="shared" si="1"/>
+        <f>E14/D14</f>
         <v>2.202436738519213</v>
       </c>
       <c r="L14" s="3">
-        <f t="shared" si="2"/>
+        <f>E14/(D14+E14)</f>
         <v>0.68773778167983612</v>
       </c>
     </row>
@@ -2848,53 +2844,53 @@
         <v>2250</v>
       </c>
       <c r="K15" s="3">
-        <f t="shared" si="1"/>
+        <f>E15/D15</f>
         <v>1.8259710586443261</v>
       </c>
       <c r="L15" s="3">
-        <f t="shared" si="2"/>
+        <f>E15/(D15+E15)</f>
         <v>0.64613933432152004</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="14">
+      <c r="A16" s="8">
         <v>1972</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="8">
         <v>5750</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="8">
         <f>G16-E16</f>
         <v>1359.99</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="8">
         <v>520.01</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="8">
         <f>C16-G16</f>
         <v>3870</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="8">
         <v>1880</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="8">
         <v>314</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="8">
         <v>1880</v>
       </c>
       <c r="K16" s="3">
-        <f t="shared" si="1"/>
+        <f>E16/D16</f>
         <v>0.38236310561107067</v>
       </c>
       <c r="L16" s="3">
-        <f t="shared" si="2"/>
+        <f>E16/(D16+E16)</f>
         <v>0.27660106382978722</v>
       </c>
     </row>
@@ -2932,53 +2928,53 @@
         <v>2267</v>
       </c>
       <c r="K17" s="3">
-        <f t="shared" si="1"/>
+        <f>E17/D17</f>
         <v>1.8259748667174411</v>
       </c>
       <c r="L17" s="3">
-        <f t="shared" si="2"/>
+        <f>E17/(D17+E17)</f>
         <v>0.64613981115778041</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="14">
+      <c r="A18" s="8">
         <v>1972</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="8">
         <v>16447</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="8">
         <v>2626</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="8">
         <v>4795.0200000000004</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="8">
         <f>C18-D18-E18</f>
         <v>9025.98</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="8">
         <f>C18-F18</f>
         <v>7421.02</v>
       </c>
-      <c r="H18" s="14" t="s">
+      <c r="H18" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="8">
         <v>311</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="8">
         <v>2265</v>
       </c>
       <c r="K18" s="3">
-        <f t="shared" si="1"/>
+        <f>E18/D18</f>
         <v>1.8259786747905562</v>
       </c>
       <c r="L18" s="3">
-        <f t="shared" si="2"/>
+        <f>E18/(D18+E18)</f>
         <v>0.64614028799275569</v>
       </c>
     </row>
@@ -3016,53 +3012,53 @@
         <v>1880</v>
       </c>
       <c r="K19" s="3">
-        <f t="shared" si="1"/>
+        <f>E19/D19</f>
         <v>0.83599999999999997</v>
       </c>
       <c r="L19" s="3">
-        <f t="shared" si="2"/>
+        <f>E19/(D19+E19)</f>
         <v>0.45533769063180829</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="14">
+      <c r="A20" s="8">
         <v>1976</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="8">
         <v>5795</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="8">
         <f>G20-E20</f>
         <v>1365</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="8">
         <v>515</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="8">
         <f>C20-G20</f>
         <v>3915</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="8">
         <v>1880</v>
       </c>
-      <c r="H20" s="14" t="s">
+      <c r="H20" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="8">
         <v>314</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="8">
         <v>1880</v>
       </c>
       <c r="K20" s="3">
-        <f t="shared" si="1"/>
+        <f>E20/D20</f>
         <v>0.37728937728937728</v>
       </c>
       <c r="L20" s="3">
-        <f t="shared" si="2"/>
+        <f>E20/(D20+E20)</f>
         <v>0.27393617021276595</v>
       </c>
     </row>
@@ -3098,51 +3094,51 @@
         <v>1880</v>
       </c>
       <c r="K21" s="3">
-        <f t="shared" si="1"/>
+        <f>E21/D21</f>
         <v>0.14166666666666666</v>
       </c>
       <c r="L21" s="3">
-        <f t="shared" si="2"/>
+        <f>E21/(D21+E21)</f>
         <v>0.12408759124087591</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="14">
+      <c r="A22" s="8">
         <v>2019</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="8">
         <v>585</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="8">
         <v>150</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="8">
         <v>0.1</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="8">
         <v>435</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="8">
         <v>150</v>
       </c>
-      <c r="H22" s="14" t="s">
+      <c r="H22" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="8">
         <v>318</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="8">
         <v>1930</v>
       </c>
       <c r="K22" s="3">
-        <f t="shared" si="1"/>
+        <f>E22/D22</f>
         <v>6.6666666666666675E-4</v>
       </c>
       <c r="L22" s="3">
-        <f t="shared" si="2"/>
+        <f>E22/(D22+E22)</f>
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
@@ -3178,51 +3174,51 @@
         <v>2000</v>
       </c>
       <c r="K23" s="3">
-        <f t="shared" si="1"/>
+        <f>E23/D23</f>
         <v>4.3130990415335461E-2</v>
       </c>
       <c r="L23" s="3">
-        <f t="shared" si="2"/>
+        <f>E23/(D23+E23)</f>
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="14">
+      <c r="A24" s="8">
         <v>2019</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="8">
         <v>3640</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="8">
         <v>1200</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="8">
         <v>170.01</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="8">
         <v>2270</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="8">
         <v>1370</v>
       </c>
-      <c r="H24" s="14" t="s">
+      <c r="H24" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="8">
         <v>333</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="8">
         <v>1880</v>
       </c>
       <c r="K24" s="3">
-        <f t="shared" si="1"/>
+        <f>E24/D24</f>
         <v>0.141675</v>
       </c>
       <c r="L24" s="3">
-        <f t="shared" si="2"/>
+        <f>E24/(D24+E24)</f>
         <v>0.12409398471544003</v>
       </c>
     </row>
@@ -3258,51 +3254,51 @@
         <v>1930</v>
       </c>
       <c r="K25" s="3">
-        <f t="shared" si="1"/>
+        <f>E25/D25</f>
         <v>0.66666666666666663</v>
       </c>
       <c r="L25" s="3">
-        <f t="shared" si="2"/>
+        <f>E25/(D25+E25)</f>
         <v>0.4</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="14">
+      <c r="A26" s="8">
         <v>2022</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="8">
         <v>14.6</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="8">
         <v>0.7</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="8">
         <v>0.10100000000000001</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F26" s="8">
         <v>13.9</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="8">
         <v>0.69999999999999929</v>
       </c>
-      <c r="H26" s="14" t="s">
+      <c r="H26" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="8">
         <v>287</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="8">
         <v>2500</v>
       </c>
       <c r="K26" s="3">
-        <f t="shared" si="1"/>
+        <f>E26/D26</f>
         <v>0.14428571428571429</v>
       </c>
       <c r="L26" s="3">
-        <f t="shared" si="2"/>
+        <f>E26/(D26+E26)</f>
         <v>0.12609238451935084</v>
       </c>
     </row>
@@ -3338,51 +3334,51 @@
         <v>2000</v>
       </c>
       <c r="K27" s="3">
-        <f t="shared" si="1"/>
+        <f>E27/D27</f>
         <v>3.896103896103896E-2</v>
       </c>
       <c r="L27" s="3">
-        <f t="shared" si="2"/>
+        <f>E27/(D27+E27)</f>
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="14">
+      <c r="A28" s="8">
         <v>2023</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="8">
         <v>1000</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="8">
         <v>340</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="8">
         <v>30.01</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="8">
         <v>630</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="8">
         <v>370</v>
       </c>
-      <c r="H28" s="14" t="s">
+      <c r="H28" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I28" s="14">
+      <c r="I28" s="8">
         <v>336</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="8">
         <v>2000</v>
       </c>
       <c r="K28" s="3">
-        <f t="shared" si="1"/>
+        <f>E28/D28</f>
         <v>8.826470588235294E-2</v>
       </c>
       <c r="L28" s="3">
-        <f t="shared" si="2"/>
+        <f>E28/(D28+E28)</f>
         <v>8.1105916056322808E-2</v>
       </c>
     </row>
@@ -3418,53 +3414,53 @@
         <v>2774</v>
       </c>
       <c r="K29" s="3">
-        <f t="shared" si="1"/>
+        <f>E29/D29</f>
         <v>0.10526315789473684</v>
       </c>
       <c r="L29" s="3">
-        <f t="shared" si="2"/>
+        <f>E29/(D29+E29)</f>
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="14">
+      <c r="A30" s="8">
         <v>2024</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="8">
         <v>1908</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="8">
         <f>675-E30</f>
         <v>545</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="8">
         <v>130</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="8">
         <v>1276</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="8">
         <f>675</f>
         <v>675</v>
       </c>
-      <c r="H30" s="14" t="s">
+      <c r="H30" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I30" s="14">
+      <c r="I30" s="8">
         <v>360</v>
       </c>
-      <c r="J30" s="14">
+      <c r="J30" s="8">
         <v>2500</v>
       </c>
       <c r="K30" s="3">
-        <f t="shared" si="1"/>
+        <f>E30/D30</f>
         <v>0.23853211009174313</v>
       </c>
       <c r="L30" s="3">
-        <f t="shared" si="2"/>
+        <f>E30/(D30+E30)</f>
         <v>0.19259259259259259</v>
       </c>
     </row>
@@ -3498,51 +3494,51 @@
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="3">
-        <f t="shared" si="1"/>
+        <f>E31/D31</f>
         <v>0.66666666666666663</v>
       </c>
       <c r="L31" s="3">
-        <f t="shared" si="2"/>
+        <f>E31/(D31+E31)</f>
         <v>0.4</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="14">
+      <c r="A32" s="8">
         <v>2025</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="8">
         <v>1517</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="8">
         <f>C32-E32-F32</f>
         <v>331</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="8">
         <v>150</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="8">
         <v>1036</v>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="8">
         <f>C32-F32</f>
         <v>481</v>
       </c>
-      <c r="H32" s="14" t="s">
+      <c r="H32" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I32" s="14">
+      <c r="I32" s="8">
         <v>340</v>
       </c>
-      <c r="J32" s="14"/>
+      <c r="J32" s="8"/>
       <c r="K32" s="3">
-        <f t="shared" si="1"/>
+        <f>E32/D32</f>
         <v>0.45317220543806647</v>
       </c>
       <c r="L32" s="3">
-        <f t="shared" si="2"/>
+        <f>E32/(D32+E32)</f>
         <v>0.31185031185031187</v>
       </c>
     </row>
@@ -3579,57 +3575,57 @@
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="3">
-        <f t="shared" si="1"/>
+        <f>E33/D33</f>
         <v>0.23853211009174313</v>
       </c>
       <c r="L33" s="3">
-        <f t="shared" si="2"/>
+        <f>E33/(D33+E33)</f>
         <v>0.19259259259259259</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="14">
+      <c r="A34" s="8">
         <v>2025</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="8">
         <v>1000</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="8">
         <v>340</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E34" s="8">
         <v>30</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="8">
         <f>C34-E34-D34</f>
         <v>630</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="8">
         <f>C34-F34</f>
         <v>370</v>
       </c>
-      <c r="H34" s="14" t="s">
+      <c r="H34" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I34" s="14">
+      <c r="I34" s="8">
         <v>336</v>
       </c>
-      <c r="J34" s="14"/>
+      <c r="J34" s="8"/>
       <c r="K34" s="3">
-        <f t="shared" si="1"/>
+        <f>E34/D34</f>
         <v>8.8235294117647065E-2</v>
       </c>
       <c r="L34" s="3">
-        <f t="shared" si="2"/>
+        <f>E34/(D34+E34)</f>
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L30">
-    <sortCondition ref="A2:A30"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L34">
+    <sortCondition ref="A2:A34"/>
   </sortState>
   <conditionalFormatting sqref="K2:K34">
     <cfRule type="colorScale" priority="23">

--- a/Lander DB 251 redux (alt).xlsx
+++ b/Lander DB 251 redux (alt).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6769C7C0-7D64-4E33-AFB1-18411BC3F5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0414E6-590A-40C0-BE6F-44498ADD148A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Real Landers" sheetId="1" r:id="rId1"/>
@@ -2286,7 +2286,7 @@
         <v>33</v>
       </c>
       <c r="F2" s="14">
-        <f>C2-D2-E2</f>
+        <f t="shared" ref="F2:F10" si="0">C2-D2-E2</f>
         <v>700.2</v>
       </c>
       <c r="G2" s="14">
@@ -2302,11 +2302,11 @@
         <v>2612</v>
       </c>
       <c r="K2" s="3">
-        <f>E2/D2</f>
+        <f t="shared" ref="K2:K34" si="1">E2/D2</f>
         <v>0.12595419847328243</v>
       </c>
       <c r="L2" s="3">
-        <f>E2/(D2+E2)</f>
+        <f t="shared" ref="L2:L34" si="2">E2/(D2+E2)</f>
         <v>0.11186440677966102</v>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>99.8</v>
       </c>
       <c r="F3" s="5">
-        <f>C3-D3-E3</f>
+        <f t="shared" si="0"/>
         <v>591.20000000000005</v>
       </c>
       <c r="G3" s="5">
@@ -2344,11 +2344,11 @@
         <v>2630</v>
       </c>
       <c r="K3" s="3">
-        <f>E3/D3</f>
+        <f t="shared" si="1"/>
         <v>0.117827626918536</v>
       </c>
       <c r="L3" s="3">
-        <f>E3/(D3+E3)</f>
+        <f t="shared" si="2"/>
         <v>0.10540768905787917</v>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
         <v>112</v>
       </c>
       <c r="F4" s="8">
-        <f>C4-D4-E4</f>
+        <f t="shared" si="0"/>
         <v>708</v>
       </c>
       <c r="G4" s="8">
@@ -2386,11 +2386,11 @@
         <v>1880</v>
       </c>
       <c r="K4" s="3">
-        <f>E4/D4</f>
+        <f t="shared" si="1"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="L4" s="3">
-        <f>E4/(D4+E4)</f>
+        <f t="shared" si="2"/>
         <v>0.12280701754385964</v>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
         <v>33.01</v>
       </c>
       <c r="F5" s="5">
-        <f>C5-D5-E5</f>
+        <f t="shared" si="0"/>
         <v>701.99</v>
       </c>
       <c r="G5" s="5">
@@ -2427,11 +2427,11 @@
         <v>2612</v>
       </c>
       <c r="K5" s="3">
-        <f>E5/D5</f>
+        <f t="shared" si="1"/>
         <v>0.12180811808118081</v>
       </c>
       <c r="L5" s="3">
-        <f>E5/(D5+E5)</f>
+        <f t="shared" si="2"/>
         <v>0.10858195454096904</v>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
         <v>33.020000000000003</v>
       </c>
       <c r="F6" s="8">
-        <f>C6-D6-E6</f>
+        <f t="shared" si="0"/>
         <v>725.98</v>
       </c>
       <c r="G6" s="8">
@@ -2468,11 +2468,11 @@
         <v>2612</v>
       </c>
       <c r="K6" s="3">
-        <f>E6/D6</f>
+        <f t="shared" si="1"/>
         <v>0.12367041198501874</v>
       </c>
       <c r="L6" s="3">
-        <f>E6/(D6+E6)</f>
+        <f t="shared" si="2"/>
         <v>0.11005932937804148</v>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
         <v>33.03</v>
       </c>
       <c r="F7" s="5">
-        <f>C7-D7-E7</f>
+        <f t="shared" si="0"/>
         <v>726.97</v>
       </c>
       <c r="G7" s="5">
@@ -2509,11 +2509,11 @@
         <v>2612</v>
       </c>
       <c r="K7" s="3">
-        <f>E7/D7</f>
+        <f t="shared" si="1"/>
         <v>0.12417293233082707</v>
       </c>
       <c r="L7" s="3">
-        <f>E7/(D7+E7)</f>
+        <f t="shared" si="2"/>
         <v>0.11045714476808348</v>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
         <v>33.04</v>
       </c>
       <c r="F8" s="8">
-        <f>C8-D8-E8</f>
+        <f t="shared" si="0"/>
         <v>732.96</v>
       </c>
       <c r="G8" s="8">
@@ -2550,11 +2550,11 @@
         <v>2612</v>
       </c>
       <c r="K8" s="3">
-        <f>E8/D8</f>
+        <f t="shared" si="1"/>
         <v>0.12102564102564102</v>
       </c>
       <c r="L8" s="3">
-        <f>E8/(D8+E8)</f>
+        <f t="shared" si="2"/>
         <v>0.10795974382433668</v>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
         <v>4819</v>
       </c>
       <c r="F9" s="5">
-        <f>C9-D9-E9</f>
+        <f t="shared" si="0"/>
         <v>8212</v>
       </c>
       <c r="G9" s="5">
@@ -2592,11 +2592,11 @@
         <v>2273</v>
       </c>
       <c r="K9" s="3">
-        <f>E9/D9</f>
+        <f t="shared" si="1"/>
         <v>2.3692232055063913</v>
       </c>
       <c r="L9" s="3">
-        <f>E9/(D9+E9)</f>
+        <f t="shared" si="2"/>
         <v>0.70319568072377059</v>
       </c>
     </row>
@@ -2617,7 +2617,7 @@
         <v>4821</v>
       </c>
       <c r="F10" s="8">
-        <f>C10-D10-E10</f>
+        <f t="shared" si="0"/>
         <v>8248</v>
       </c>
       <c r="G10" s="8">
@@ -2634,11 +2634,11 @@
         <v>2261</v>
       </c>
       <c r="K10" s="3">
-        <f>E10/D10</f>
+        <f t="shared" si="1"/>
         <v>2.3702064896755162</v>
       </c>
       <c r="L10" s="3">
-        <f>E10/(D10+E10)</f>
+        <f t="shared" si="2"/>
         <v>0.70328227571115975</v>
       </c>
     </row>
@@ -2676,11 +2676,11 @@
         <v>1880</v>
       </c>
       <c r="K11" s="3">
-        <f>E11/D11</f>
+        <f t="shared" si="1"/>
         <v>0.38235294117647056</v>
       </c>
       <c r="L11" s="3">
-        <f>E11/(D11+E11)</f>
+        <f t="shared" si="2"/>
         <v>0.27659574468085107</v>
       </c>
     </row>
@@ -2718,11 +2718,11 @@
         <v>1880</v>
       </c>
       <c r="K12" s="3">
-        <f>E12/D12</f>
+        <f t="shared" si="1"/>
         <v>0.66083916083916083</v>
       </c>
       <c r="L12" s="3">
-        <f>E12/(D12+E12)</f>
+        <f t="shared" si="2"/>
         <v>0.39789473684210525</v>
       </c>
     </row>
@@ -2760,11 +2760,11 @@
         <v>2263</v>
       </c>
       <c r="K13" s="3">
-        <f>E13/D13</f>
+        <f t="shared" si="1"/>
         <v>2.1284969179706024</v>
       </c>
       <c r="L13" s="3">
-        <f>E13/(D13+E13)</f>
+        <f t="shared" si="2"/>
         <v>0.68035768414671116</v>
       </c>
     </row>
@@ -2802,11 +2802,11 @@
         <v>2263</v>
       </c>
       <c r="K14" s="3">
-        <f>E14/D14</f>
+        <f t="shared" si="1"/>
         <v>2.202436738519213</v>
       </c>
       <c r="L14" s="3">
-        <f>E14/(D14+E14)</f>
+        <f t="shared" si="2"/>
         <v>0.68773778167983612</v>
       </c>
     </row>
@@ -2844,11 +2844,11 @@
         <v>2250</v>
       </c>
       <c r="K15" s="3">
-        <f>E15/D15</f>
+        <f t="shared" si="1"/>
         <v>1.8259710586443261</v>
       </c>
       <c r="L15" s="3">
-        <f>E15/(D15+E15)</f>
+        <f t="shared" si="2"/>
         <v>0.64613933432152004</v>
       </c>
     </row>
@@ -2886,11 +2886,11 @@
         <v>1880</v>
       </c>
       <c r="K16" s="3">
-        <f>E16/D16</f>
+        <f t="shared" si="1"/>
         <v>0.38236310561107067</v>
       </c>
       <c r="L16" s="3">
-        <f>E16/(D16+E16)</f>
+        <f t="shared" si="2"/>
         <v>0.27660106382978722</v>
       </c>
     </row>
@@ -2928,11 +2928,11 @@
         <v>2267</v>
       </c>
       <c r="K17" s="3">
-        <f>E17/D17</f>
+        <f t="shared" si="1"/>
         <v>1.8259748667174411</v>
       </c>
       <c r="L17" s="3">
-        <f>E17/(D17+E17)</f>
+        <f t="shared" si="2"/>
         <v>0.64613981115778041</v>
       </c>
     </row>
@@ -2970,11 +2970,11 @@
         <v>2265</v>
       </c>
       <c r="K18" s="3">
-        <f>E18/D18</f>
+        <f t="shared" si="1"/>
         <v>1.8259786747905562</v>
       </c>
       <c r="L18" s="3">
-        <f>E18/(D18+E18)</f>
+        <f t="shared" si="2"/>
         <v>0.64614028799275569</v>
       </c>
     </row>
@@ -3012,11 +3012,11 @@
         <v>1880</v>
       </c>
       <c r="K19" s="3">
-        <f>E19/D19</f>
+        <f t="shared" si="1"/>
         <v>0.83599999999999997</v>
       </c>
       <c r="L19" s="3">
-        <f>E19/(D19+E19)</f>
+        <f t="shared" si="2"/>
         <v>0.45533769063180829</v>
       </c>
     </row>
@@ -3054,11 +3054,11 @@
         <v>1880</v>
       </c>
       <c r="K20" s="3">
-        <f>E20/D20</f>
+        <f t="shared" si="1"/>
         <v>0.37728937728937728</v>
       </c>
       <c r="L20" s="3">
-        <f>E20/(D20+E20)</f>
+        <f t="shared" si="2"/>
         <v>0.27393617021276595</v>
       </c>
     </row>
@@ -3094,11 +3094,11 @@
         <v>1880</v>
       </c>
       <c r="K21" s="3">
-        <f>E21/D21</f>
+        <f t="shared" si="1"/>
         <v>0.14166666666666666</v>
       </c>
       <c r="L21" s="3">
-        <f>E21/(D21+E21)</f>
+        <f t="shared" si="2"/>
         <v>0.12408759124087591</v>
       </c>
     </row>
@@ -3134,11 +3134,11 @@
         <v>1930</v>
       </c>
       <c r="K22" s="3">
-        <f>E22/D22</f>
+        <f t="shared" si="1"/>
         <v>6.6666666666666675E-4</v>
       </c>
       <c r="L22" s="3">
-        <f>E22/(D22+E22)</f>
+        <f t="shared" si="2"/>
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
@@ -3174,11 +3174,11 @@
         <v>2000</v>
       </c>
       <c r="K23" s="3">
-        <f>E23/D23</f>
+        <f t="shared" si="1"/>
         <v>4.3130990415335461E-2</v>
       </c>
       <c r="L23" s="3">
-        <f>E23/(D23+E23)</f>
+        <f t="shared" si="2"/>
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
@@ -3214,11 +3214,11 @@
         <v>1880</v>
       </c>
       <c r="K24" s="3">
-        <f>E24/D24</f>
+        <f t="shared" si="1"/>
         <v>0.141675</v>
       </c>
       <c r="L24" s="3">
-        <f>E24/(D24+E24)</f>
+        <f t="shared" si="2"/>
         <v>0.12409398471544003</v>
       </c>
     </row>
@@ -3254,11 +3254,11 @@
         <v>1930</v>
       </c>
       <c r="K25" s="3">
-        <f>E25/D25</f>
+        <f t="shared" si="1"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="L25" s="3">
-        <f>E25/(D25+E25)</f>
+        <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
     </row>
@@ -3294,11 +3294,11 @@
         <v>2500</v>
       </c>
       <c r="K26" s="3">
-        <f>E26/D26</f>
+        <f t="shared" si="1"/>
         <v>0.14428571428571429</v>
       </c>
       <c r="L26" s="3">
-        <f>E26/(D26+E26)</f>
+        <f t="shared" si="2"/>
         <v>0.12609238451935084</v>
       </c>
     </row>
@@ -3334,11 +3334,11 @@
         <v>2000</v>
       </c>
       <c r="K27" s="3">
-        <f>E27/D27</f>
+        <f t="shared" si="1"/>
         <v>3.896103896103896E-2</v>
       </c>
       <c r="L27" s="3">
-        <f>E27/(D27+E27)</f>
+        <f t="shared" si="2"/>
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
@@ -3374,11 +3374,11 @@
         <v>2000</v>
       </c>
       <c r="K28" s="3">
-        <f>E28/D28</f>
+        <f t="shared" si="1"/>
         <v>8.826470588235294E-2</v>
       </c>
       <c r="L28" s="3">
-        <f>E28/(D28+E28)</f>
+        <f t="shared" si="2"/>
         <v>8.1105916056322808E-2</v>
       </c>
     </row>
@@ -3414,11 +3414,11 @@
         <v>2774</v>
       </c>
       <c r="K29" s="3">
-        <f>E29/D29</f>
+        <f t="shared" si="1"/>
         <v>0.10526315789473684</v>
       </c>
       <c r="L29" s="3">
-        <f>E29/(D29+E29)</f>
+        <f t="shared" si="2"/>
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
@@ -3456,11 +3456,11 @@
         <v>2500</v>
       </c>
       <c r="K30" s="3">
-        <f>E30/D30</f>
+        <f t="shared" si="1"/>
         <v>0.23853211009174313</v>
       </c>
       <c r="L30" s="3">
-        <f>E30/(D30+E30)</f>
+        <f t="shared" si="2"/>
         <v>0.19259259259259259</v>
       </c>
     </row>
@@ -3494,11 +3494,11 @@
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="3">
-        <f>E31/D31</f>
+        <f t="shared" si="1"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="L31" s="3">
-        <f>E31/(D31+E31)</f>
+        <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
     </row>
@@ -3534,11 +3534,11 @@
       </c>
       <c r="J32" s="8"/>
       <c r="K32" s="3">
-        <f>E32/D32</f>
+        <f t="shared" si="1"/>
         <v>0.45317220543806647</v>
       </c>
       <c r="L32" s="3">
-        <f>E32/(D32+E32)</f>
+        <f t="shared" si="2"/>
         <v>0.31185031185031187</v>
       </c>
     </row>
@@ -3575,11 +3575,11 @@
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="3">
-        <f>E33/D33</f>
+        <f t="shared" si="1"/>
         <v>0.23853211009174313</v>
       </c>
       <c r="L33" s="3">
-        <f>E33/(D33+E33)</f>
+        <f t="shared" si="2"/>
         <v>0.19259259259259259</v>
       </c>
     </row>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="J34" s="8"/>
       <c r="K34" s="3">
-        <f>E34/D34</f>
+        <f t="shared" si="1"/>
         <v>8.8235294117647065E-2</v>
       </c>
       <c r="L34" s="3">
-        <f>E34/(D34+E34)</f>
+        <f t="shared" si="2"/>
         <v>8.1081081081081086E-2</v>
       </c>
     </row>

--- a/Lander DB 251 redux (alt).xlsx
+++ b/Lander DB 251 redux (alt).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0414E6-590A-40C0-BE6F-44498ADD148A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910DE151-AABA-4D6D-9E8B-2E2417A77BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="744" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Real Landers" sheetId="1" r:id="rId1"/>
@@ -2218,20 +2218,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
         <v>1966</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>1966</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>1967</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>0.10858195454096904</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>1967</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>0.11005932937804148</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>0.11045714476808348</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>0.10795974382433668</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>1969</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>0.70319568072377059</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>1969</v>
       </c>
@@ -2642,7 +2642,7 @@
         <v>0.70328227571115975</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>1970</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>1970</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>1970</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>0.68035768414671116</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>1971</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>0.68773778167983612</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>1971</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>0.64613933432152004</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>1972</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>0.27660106382978722</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>1972</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>0.64613981115778041</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>1972</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>0.64614028799275569</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>1973</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>1976</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>2013</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>2019</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>2019</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>2019</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>0.12409398471544003</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>2020</v>
       </c>
@@ -3262,7 +3262,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>2022</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>0.12609238451935084</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>2023</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>2023</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>8.1105916056322808E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>2024</v>
       </c>
@@ -3422,7 +3422,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>2024</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>0.19259259259259259</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>2024</v>
       </c>
@@ -3492,7 +3492,9 @@
       <c r="I31" s="5">
         <v>333</v>
       </c>
-      <c r="J31" s="5"/>
+      <c r="J31" s="5">
+        <v>1930</v>
+      </c>
       <c r="K31" s="3">
         <f t="shared" si="1"/>
         <v>0.66666666666666663</v>
@@ -3502,7 +3504,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>2025</v>
       </c>
@@ -3542,7 +3544,7 @@
         <v>0.31185031185031187</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>2025</v>
       </c>
@@ -3583,7 +3585,7 @@
         <v>0.19259259259259259</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>2025</v>
       </c>
@@ -3655,9 +3657,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9B5FE63-1677-42A4-8B75-DD4C8D8979A4}">
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3695,7 +3697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>1966</v>
       </c>
@@ -3737,7 +3739,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -3779,7 +3781,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -3820,7 +3822,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>1967</v>
       </c>
@@ -3861,7 +3863,7 @@
         <v>0.10855263157894737</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>1967</v>
       </c>
@@ -3902,7 +3904,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -3943,7 +3945,7 @@
         <v>0.11036789297658862</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -3984,7 +3986,7 @@
         <v>0.10784313725490197</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>1969</v>
       </c>
@@ -4026,7 +4028,7 @@
         <v>0.70328227571115975</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>1969</v>
       </c>
@@ -4068,7 +4070,7 @@
         <v>0.70319568072377059</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>1970</v>
       </c>
@@ -4110,7 +4112,7 @@
         <v>0.68035768414671116</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>1970</v>
       </c>
@@ -4152,7 +4154,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>1970</v>
       </c>
@@ -4194,7 +4196,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>1971</v>
       </c>
@@ -4236,7 +4238,7 @@
         <v>0.64613933432152004</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>1971</v>
       </c>
@@ -4278,7 +4280,7 @@
         <v>0.68773778167983612</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>1972</v>
       </c>
@@ -4320,7 +4322,7 @@
         <v>0.64613933432152004</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>1972</v>
       </c>
@@ -4362,7 +4364,7 @@
         <v>0.64613933432152004</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>1972</v>
       </c>
@@ -4404,7 +4406,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>1973</v>
       </c>
@@ -4440,7 +4442,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>1976</v>
       </c>
@@ -4482,7 +4484,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>2013</v>
       </c>
@@ -4522,7 +4524,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>2019</v>
       </c>
@@ -4562,7 +4564,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>2019</v>
       </c>
@@ -4600,7 +4602,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>2019</v>
       </c>
@@ -4640,7 +4642,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>2020</v>
       </c>
@@ -4680,7 +4682,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>2022</v>
       </c>
@@ -4718,7 +4720,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>2023</v>
       </c>
@@ -4756,7 +4758,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>2023</v>
       </c>
@@ -4794,7 +4796,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>2023</v>
       </c>
@@ -4821,7 +4823,7 @@
       <c r="J29" s="7"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>2024</v>
       </c>
@@ -4854,7 +4856,7 @@
       <c r="J30" s="10"/>
       <c r="K30" s="3"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>2024</v>
       </c>
@@ -4881,7 +4883,7 @@
       <c r="J31" s="7"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>2024</v>
       </c>
@@ -4950,12 +4952,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB6D447-256B-4552-8531-20A905B8B356}">
   <dimension ref="A1:L23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4993,7 +4995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1966</v>
       </c>
@@ -5035,7 +5037,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -5077,7 +5079,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -5118,7 +5120,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>1967</v>
       </c>
@@ -5159,7 +5161,7 @@
         <v>0.10855263157894737</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>1967</v>
       </c>
@@ -5200,7 +5202,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -5241,7 +5243,7 @@
         <v>0.11036789297658862</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -5282,7 +5284,7 @@
         <v>0.10784313725490197</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>1970</v>
       </c>
@@ -5324,7 +5326,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>1970</v>
       </c>
@@ -5366,7 +5368,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>1972</v>
       </c>
@@ -5408,7 +5410,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>1973</v>
       </c>
@@ -5450,7 +5452,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>1976</v>
       </c>
@@ -5492,7 +5494,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>2013</v>
       </c>
@@ -5532,7 +5534,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>2019</v>
       </c>
@@ -5572,7 +5574,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>2019</v>
       </c>
@@ -5610,7 +5612,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>2019</v>
       </c>
@@ -5650,7 +5652,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>2020</v>
       </c>
@@ -5690,7 +5692,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>2022</v>
       </c>
@@ -5728,7 +5730,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>2023</v>
       </c>
@@ -5766,7 +5768,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>2023</v>
       </c>
@@ -5804,7 +5806,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>2024</v>
       </c>
@@ -5844,7 +5846,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>2024</v>
       </c>
@@ -5929,7 +5931,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21568D6A-64F0-4E55-9F6A-12E6ECCA0346}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5938,9 +5940,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05661A04-FF2A-413A-B709-071725466C45}">
   <dimension ref="A1:L16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5978,7 +5980,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1966</v>
       </c>
@@ -6020,7 +6022,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -6062,7 +6064,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -6103,7 +6105,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>1970</v>
       </c>
@@ -6145,7 +6147,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>1970</v>
       </c>
@@ -6187,7 +6189,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>1973</v>
       </c>
@@ -6229,7 +6231,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>1976</v>
       </c>
@@ -6271,7 +6273,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>2019</v>
       </c>
@@ -6309,7 +6311,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>2019</v>
       </c>
@@ -6349,7 +6351,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>2020</v>
       </c>
@@ -6389,7 +6391,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>2022</v>
       </c>
@@ -6427,7 +6429,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>2023</v>
       </c>
@@ -6465,7 +6467,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>2023</v>
       </c>
@@ -6503,7 +6505,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>2024</v>
       </c>
@@ -6543,7 +6545,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>2024</v>
       </c>

--- a/Lander DB 251 redux (alt).xlsx
+++ b/Lander DB 251 redux (alt).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910DE151-AABA-4D6D-9E8B-2E2417A77BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACAC3BF-309F-4540-A714-7F67E641F9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="744" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Real Landers" sheetId="1" r:id="rId1"/>
@@ -1769,7 +1769,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1791,6 +1791,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1846,7 +1852,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1883,6 +1889,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2217,7 +2226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
@@ -2894,7 +2903,7 @@
         <v>0.27660106382978722</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>1972</v>
       </c>
@@ -2936,7 +2945,7 @@
         <v>0.64613981115778041</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>1972</v>
       </c>
@@ -2978,7 +2987,7 @@
         <v>0.64614028799275569</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>1973</v>
       </c>
@@ -3020,7 +3029,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>1976</v>
       </c>
@@ -3062,7 +3071,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>2013</v>
       </c>
@@ -3102,7 +3111,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>2019</v>
       </c>
@@ -3142,7 +3151,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>2019</v>
       </c>
@@ -3182,7 +3191,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>2019</v>
       </c>
@@ -3222,7 +3231,7 @@
         <v>0.12409398471544003</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>2020</v>
       </c>
@@ -3262,7 +3271,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>2022</v>
       </c>
@@ -3302,7 +3311,7 @@
         <v>0.12609238451935084</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>2023</v>
       </c>
@@ -3342,7 +3351,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>2023</v>
       </c>
@@ -3382,7 +3391,7 @@
         <v>8.1105916056322808E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>2024</v>
       </c>
@@ -3422,7 +3431,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>2024</v>
       </c>
@@ -3463,8 +3472,12 @@
         <f t="shared" si="2"/>
         <v>0.19259259259259259</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N30">
+        <f>325*9.81*LN((C30)/(D30+E30))</f>
+        <v>3312.904712240902</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>2024</v>
       </c>
@@ -3504,7 +3517,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>2025</v>
       </c>
@@ -3534,7 +3547,9 @@
       <c r="I32" s="8">
         <v>340</v>
       </c>
-      <c r="J32" s="8"/>
+      <c r="J32" s="16">
+        <v>2500</v>
+      </c>
       <c r="K32" s="3">
         <f t="shared" si="1"/>
         <v>0.45317220543806647</v>
@@ -3575,7 +3590,9 @@
       <c r="I33" s="5">
         <v>360</v>
       </c>
-      <c r="J33" s="5"/>
+      <c r="J33" s="16">
+        <v>2500</v>
+      </c>
       <c r="K33" s="3">
         <f t="shared" si="1"/>
         <v>0.23853211009174313</v>
@@ -3615,7 +3632,9 @@
       <c r="I34" s="8">
         <v>336</v>
       </c>
-      <c r="J34" s="8"/>
+      <c r="J34" s="16">
+        <v>2500</v>
+      </c>
       <c r="K34" s="3">
         <f t="shared" si="1"/>
         <v>8.8235294117647065E-2</v>
